--- a/西雙版納·普洱每日行程資料.xlsx
+++ b/西雙版納·普洱每日行程資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangzhiyin/Downloads/西雙版納·普洱-7天6晚自由行攻略/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989E5BD0-10ED-E64D-B485-659A98D11721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91AB976-D7F4-2C4D-91ED-B98E67852E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
   <si>
     <t>活動名稱</t>
   </si>
@@ -74,9 +74,6 @@
     <t>中科院熱帶植物園</t>
   </si>
   <si>
-    <t>包車 / 拼車</t>
-  </si>
-  <si>
     <t>白天</t>
   </si>
   <si>
@@ -86,18 +83,6 @@
     <t>傍晚</t>
   </si>
   <si>
-    <t>車程約 1–1.5 小時，返回告庄休息。</t>
-  </si>
-  <si>
-    <t>告庄西雙景夜市</t>
-  </si>
-  <si>
-    <t>夜市覓食，沿瀾滄江散步。</t>
-  </si>
-  <si>
-    <t>版納租車取車</t>
-  </si>
-  <si>
     <t>2025-10-15</t>
   </si>
   <si>
@@ -107,9 +92,6 @@
     <t>租車自駕</t>
   </si>
   <si>
-    <t>辦理租車手續、檢查車況，自駕出發前往有風咖谷。</t>
-  </si>
-  <si>
     <t>有風咖谷</t>
   </si>
   <si>
@@ -343,35 +325,83 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>前往中科院西雙版納熱帶植物園（國家 5A 景區）。交通：景洪 → 勐侖約 1–1.5 小時</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>上午 08:00</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>回</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>汉庭西双版纳曼听御花园酒店</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>晚上</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>東區原始雨林</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> + 西區園林</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>返回景洪</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早餐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>汉庭酒店(西双版纳孔雀湖店)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 西區園林</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>東區原始雨林徒步</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下午</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>约一个小时车程</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:30-07:00 左右出发。早餐视前一晚而定：①买面包；②点外卖（注意外卖的预计送达时间）；③楼下附近吃（不累&amp;能起床的话）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上午 07:00</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以去附近的烧烤，如果累的话可以去按摩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>⚠️最晚不能超过17点走</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下午16:30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游览车</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游览车/步行</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果很累就买观光车（50r）。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回程休息</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>出发普洱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>高铁</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -427,7 +457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -444,7 +474,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -455,10 +484,10 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -492,15 +521,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DailyItinerarySource" displayName="DailyItinerarySource" ref="A1:F27" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:F27" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DailyItinerarySource" displayName="DailyItinerarySource" ref="A1:F28" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F28" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="活動名稱" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="日期" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="時間段" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="關聯行程" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="交通方式" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="備註" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="交通方式" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="備註" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -714,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27.5" style="4" bestFit="1" customWidth="1"/>
@@ -722,9 +751,8 @@
     <col min="3" max="3" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.5" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="63" style="6" customWidth="1"/>
-    <col min="7" max="7" width="72" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="6"/>
+    <col min="6" max="6" width="63" customWidth="1"/>
+    <col min="7" max="7" width="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
@@ -748,505 +776,529 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="34" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>97</v>
+      <c r="A2" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="B2" s="3">
         <v>46308</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>93</v>
+      <c r="E2" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>95</v>
+      <c r="A3" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="B3" s="3">
         <v>46308</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>94</v>
+      <c r="E3" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="34" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="3">
         <v>46308</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>94</v>
+      <c r="E4" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="34" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>99</v>
+      <c r="A5" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B5" s="3">
         <v>46308</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="6" spans="1:6" ht="34" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>106</v>
+      <c r="A6" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="B6" s="3">
         <v>46308</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="34" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>13</v>
+      <c r="A7" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="B7" s="3">
         <v>46309</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>102</v>
-      </c>
+      <c r="C7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>108</v>
+      <c r="A8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>46309</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="F8" s="2" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>109</v>
+      <c r="A9" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="B9" s="3">
         <v>46309</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
+      <c r="E9" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="34" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>22</v>
+      <c r="A11" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="B11" s="3">
         <v>46309</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="34" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="D12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="34" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46310</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>27</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="34" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>29</v>
+      <c r="A13" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="B13" s="3">
         <v>46310</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="C13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="34" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>31</v>
+      <c r="A14" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B14" s="3">
         <v>46310</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>27</v>
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="34" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>33</v>
+      <c r="A15" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B15" s="3">
         <v>46310</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="34" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="34" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46311</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>39</v>
+      <c r="D16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="34" customHeight="1">
-      <c r="A17" s="7" t="s">
-        <v>41</v>
+      <c r="A17" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B17" s="3">
         <v>46311</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>42</v>
+      <c r="C17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="34" customHeight="1">
-      <c r="A18" s="7" t="s">
-        <v>44</v>
+      <c r="A18" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="B18" s="3">
         <v>46311</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="34" customHeight="1">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="B19" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="34" customHeight="1">
-      <c r="A19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="3">
-        <v>46312</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="20" spans="1:6" ht="34" customHeight="1">
-      <c r="A20" s="7" t="s">
-        <v>51</v>
+      <c r="A20" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="B20" s="3">
         <v>46312</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>12</v>
+      <c r="C20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="34" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>53</v>
+      <c r="A21" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="B21" s="3">
         <v>46312</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="34" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46312</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="34" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="3">
-        <v>46313</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="23" spans="1:6" ht="34" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>60</v>
+      <c r="A23" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B23" s="3">
         <v>46313</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>49</v>
+      <c r="C23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>62</v>
+      <c r="A24" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="B24" s="3">
         <v>46313</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="34" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46313</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="34" customHeight="1">
+      <c r="A26" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="34" customHeight="1">
-      <c r="A25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="3">
-        <v>46314</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="34" customHeight="1">
-      <c r="A26" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="B26" s="3">
         <v>46314</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>8</v>
+      <c r="C26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="34" customHeight="1">
-      <c r="A27" s="7" t="s">
-        <v>70</v>
+      <c r="A27" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B27" s="3">
         <v>46314</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="34" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="D28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>71</v>
+      <c r="F28" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1273,16 +1325,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -1290,121 +1342,121 @@
     </row>
     <row r="2" spans="1:5" ht="32" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="32" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/西雙版納·普洱每日行程資料.xlsx
+++ b/西雙版納·普洱每日行程資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangzhiyin/Downloads/西雙版納·普洱-7天6晚自由行攻略/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91AB976-D7F4-2C4D-91ED-B98E67852E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390C4739-CED1-2F40-91A6-D0CC3D39DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/西雙版納·普洱每日行程資料.xlsx
+++ b/西雙版納·普洱每日行程資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangzhiyin/Downloads/西雙版納·普洱-7天6晚自由行攻略/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390C4739-CED1-2F40-91A6-D0CC3D39DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47EBD35-EBEB-0341-AFDD-610E2C38BB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="117">
   <si>
     <t>活動名稱</t>
   </si>
@@ -879,7 +879,9 @@
       <c r="C7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="2" t="s">
         <v>106</v>
@@ -955,7 +957,9 @@
       <c r="C11" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="6" t="s">
         <v>96</v>
       </c>

--- a/西雙版納·普洱每日行程資料.xlsx
+++ b/西雙版納·普洱每日行程資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangzhiyin/Downloads/西雙版納·普洱-7天6晚自由行攻略/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47EBD35-EBEB-0341-AFDD-610E2C38BB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F5C427-7222-3B41-A40A-E631D3082C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="118">
   <si>
     <t>活動名稱</t>
   </si>
@@ -86,9 +86,6 @@
     <t>2025-10-15</t>
   </si>
   <si>
-    <t>租車自駕 → 有風咖谷 → 普洱</t>
-  </si>
-  <si>
     <t>租車自駕</t>
   </si>
   <si>
@@ -98,12 +95,6 @@
     <t>咖啡主題山谷，可體驗咖啡採摘 / 手沖，欣賞山谷風光。</t>
   </si>
   <si>
-    <t>驅車前往普洱</t>
-  </si>
-  <si>
-    <t>前往普洱市區，抵達後辦理異地還車。交通：版納 → 普洱約 3–4 小時（含沿途景點）</t>
-  </si>
-  <si>
     <t>宿普洱市區 · 茶馬古城</t>
   </si>
   <si>
@@ -197,211 +188,228 @@
     <t>傣族古寨與千年古茶園，林中有茶、茶中有林，可品古樹茶。</t>
   </si>
   <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>回版納 · 按摩放鬆 · 返程</t>
+  </si>
+  <si>
+    <t>由景邁山返回版納市區，途中可停留拍照。交通：約 3–3.5 小時</t>
+  </si>
+  <si>
+    <t>泰式 / 傣式按摩放鬆</t>
+  </si>
+  <si>
+    <t>按摩舒緩旅途疲勞，整理行李、採買伴手禮。</t>
+  </si>
+  <si>
+    <t>從西雙版納出發返程</t>
+  </si>
+  <si>
+    <t>提前 2–3 小時抵達機場辦理手續。交通：市區 → 嘎洒機場約 20–30 分鐘</t>
+  </si>
+  <si>
+    <t>名稱</t>
+  </si>
+  <si>
+    <t>類別</t>
+  </si>
+  <si>
+    <t>入住或用餐日期</t>
+  </si>
+  <si>
+    <t>推薦菜或房型</t>
+  </si>
+  <si>
+    <t>Day1 餐食建議</t>
+  </si>
+  <si>
+    <t>餐飲</t>
+  </si>
+  <si>
+    <t>晚餐：星光夜市傣味小吃、燒烤</t>
+  </si>
+  <si>
+    <t>按每日行程整理</t>
+  </si>
+  <si>
+    <t>Day2 餐食建議</t>
+  </si>
+  <si>
+    <t>午餐：園區簡餐 / 自備乾糧；晚餐：告庄夜市</t>
+  </si>
+  <si>
+    <t>Day3 餐食建議</t>
+  </si>
+  <si>
+    <t>午餐：有風咖谷 / 沿途；晚餐：普洱市區茶鄉菜</t>
+  </si>
+  <si>
+    <t>Day4 餐食建議</t>
+  </si>
+  <si>
+    <t>午餐：太陽河周邊；晚餐：普洱市區酸筍雞</t>
+  </si>
+  <si>
+    <t>Day5 餐食建議</t>
+  </si>
+  <si>
+    <t>午餐：沿途 / 古寨農家菜；晚餐：古寨茶山菜</t>
+  </si>
+  <si>
+    <t>Day6 餐食建議</t>
+  </si>
+  <si>
+    <t>午餐 / 晚餐：古寨農家菜</t>
+  </si>
+  <si>
+    <t>Day7 餐食建議</t>
+  </si>
+  <si>
+    <t>午餐 / 晚餐：版納市區餐廳，出發前簡單用餐</t>
+  </si>
+  <si>
+    <t>中午</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>联系酒店接送机</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>电动车</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>午饭时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10月13日06:40，广州白云国际机场T2至西双版纳嘎洒国际机场T1的AQ1041航班。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵達西双版纳嘎洒国际机场T1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>景点选择</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>江边夜市 / 星光夜市</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>江边夜市注意看傣锦冰箱贴；晚饭看是吃烧烤还是路摊贩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上午 09:20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>滴滴巴士</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上午 08:00</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回景洪</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早餐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>汉庭酒店(西双版纳孔雀湖店)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 西區園林</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>東區原始雨林徒步</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下午</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>约一个小时车程</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:30-07:00 左右出发。早餐视前一晚而定：①买面包；②点外卖（注意外卖的预计送达时间）；③楼下附近吃（不累&amp;能起床的话）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上午 07:00</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以去附近的烧烤，如果累的话可以去按摩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>⚠️最晚不能超过17点走</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下午16:30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游览车</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游览车/步行</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果很累就买观光车（50r）。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回程休息</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普洱闲逛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上午 07:30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>西双版纳自驾-普洱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>去租车点提车，自驾到普洱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>返回西雙版納</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>回版納 · 按摩放鬆 · 返程</t>
-  </si>
-  <si>
-    <t>由景邁山返回版納市區，途中可停留拍照。交通：約 3–3.5 小時</t>
-  </si>
-  <si>
-    <t>泰式 / 傣式按摩放鬆</t>
-  </si>
-  <si>
-    <t>按摩舒緩旅途疲勞，整理行李、採買伴手禮。</t>
-  </si>
-  <si>
-    <t>從西雙版納出發返程</t>
-  </si>
-  <si>
-    <t>提前 2–3 小時抵達機場辦理手續。交通：市區 → 嘎洒機場約 20–30 分鐘</t>
-  </si>
-  <si>
-    <t>名稱</t>
-  </si>
-  <si>
-    <t>類別</t>
-  </si>
-  <si>
-    <t>入住或用餐日期</t>
-  </si>
-  <si>
-    <t>推薦菜或房型</t>
-  </si>
-  <si>
-    <t>Day1 餐食建議</t>
-  </si>
-  <si>
-    <t>餐飲</t>
-  </si>
-  <si>
-    <t>晚餐：星光夜市傣味小吃、燒烤</t>
-  </si>
-  <si>
-    <t>按每日行程整理</t>
-  </si>
-  <si>
-    <t>Day2 餐食建議</t>
-  </si>
-  <si>
-    <t>午餐：園區簡餐 / 自備乾糧；晚餐：告庄夜市</t>
-  </si>
-  <si>
-    <t>Day3 餐食建議</t>
-  </si>
-  <si>
-    <t>午餐：有風咖谷 / 沿途；晚餐：普洱市區茶鄉菜</t>
-  </si>
-  <si>
-    <t>Day4 餐食建議</t>
-  </si>
-  <si>
-    <t>午餐：太陽河周邊；晚餐：普洱市區酸筍雞</t>
-  </si>
-  <si>
-    <t>Day5 餐食建議</t>
-  </si>
-  <si>
-    <t>午餐：沿途 / 古寨農家菜；晚餐：古寨茶山菜</t>
-  </si>
-  <si>
-    <t>Day6 餐食建議</t>
-  </si>
-  <si>
-    <t>午餐 / 晚餐：古寨農家菜</t>
-  </si>
-  <si>
-    <t>Day7 餐食建議</t>
-  </si>
-  <si>
-    <t>午餐 / 晚餐：版納市區餐廳，出發前簡單用餐</t>
-  </si>
-  <si>
-    <t>中午</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>联系酒店接送机</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>电动车</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>午饭时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10月13日06:40，广州白云国际机场T2至西双版纳嘎洒国际机场T1的AQ1041航班。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵達西双版纳嘎洒国际机场T1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>景点选择</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>江边夜市 / 星光夜市</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>江边夜市注意看傣锦冰箱贴；晚饭看是吃烧烤还是路摊贩</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上午 09:20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>滴滴巴士</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上午 08:00</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>晚上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回景洪</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>早餐</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>汉庭酒店(西双版纳孔雀湖店)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 西區園林</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>東區原始雨林徒步</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>下午</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>约一个小时车程</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>06:30-07:00 左右出发。早餐视前一晚而定：①买面包；②点外卖（注意外卖的预计送达时间）；③楼下附近吃（不累&amp;能起床的话）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上午 07:00</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以去附近的烧烤，如果累的话可以去按摩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>⚠️最晚不能超过17点走</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>下午16:30</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>游览车</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>游览车/步行</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果很累就买观光车（50r）。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>回程休息</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>出发普洱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>高铁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下午 15:00-16:00</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>市区CityWalk</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -409,7 +417,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -429,6 +437,11 @@
       <name val="FangSong"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -457,7 +470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -476,6 +489,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -777,39 +799,39 @@
     </row>
     <row r="2" spans="1:6" ht="34" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B2" s="3">
         <v>46308</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="34" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3">
         <v>46308</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -827,15 +849,15 @@
         <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="34" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>46308</v>
@@ -847,21 +869,21 @@
         <v>7</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="34" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3">
         <v>46308</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>7</v>
@@ -871,20 +893,20 @@
     </row>
     <row r="7" spans="1:6" ht="34" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B7" s="3">
         <v>46309</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" customHeight="1">
@@ -895,21 +917,21 @@
         <v>46309</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B9" s="3">
         <v>46309</v>
@@ -921,7 +943,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
@@ -929,47 +951,47 @@
     </row>
     <row r="10" spans="1:6" ht="34" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B10" s="3">
         <v>46309</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3">
         <v>46309</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="34" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3">
         <v>46309</v>
@@ -978,116 +1000,116 @@
         <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="34" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="3">
+      <c r="A13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="8">
         <v>46310</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="34" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="8">
+        <v>46310</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="34" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46310</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="34" customHeight="1">
-      <c r="A14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="D15" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" ht="34" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="8">
         <v>46310</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="34" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="C16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="3">
-        <v>46310</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="F16" s="9" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="34" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46310</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="34" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B17" s="3">
         <v>46311</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="34" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B18" s="3">
         <v>46311</v>
@@ -1096,18 +1118,18 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="34" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B19" s="3">
         <v>46311</v>
@@ -1116,18 +1138,18 @@
         <v>19</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="34" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B20" s="3">
         <v>46312</v>
@@ -1136,18 +1158,18 @@
         <v>15</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="34" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" s="3">
         <v>46312</v>
@@ -1156,18 +1178,18 @@
         <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="34" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B22" s="3">
         <v>46312</v>
@@ -1176,38 +1198,38 @@
         <v>19</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="34" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B23" s="3">
         <v>46313</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3">
         <v>46313</v>
@@ -1216,18 +1238,18 @@
         <v>15</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="34" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3">
         <v>46313</v>
@@ -1236,18 +1258,18 @@
         <v>10</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="34" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="B26" s="3">
         <v>46314</v>
@@ -1256,18 +1278,18 @@
         <v>15</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="34" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B27" s="3">
         <v>46314</v>
@@ -1276,18 +1298,18 @@
         <v>10</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B28" s="3">
         <v>46314</v>
@@ -1296,13 +1318,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1329,16 +1351,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -1346,121 +1368,121 @@
     </row>
     <row r="2" spans="1:5" ht="32" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="32" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/西雙版納·普洱每日行程資料.xlsx
+++ b/西雙版納·普洱每日行程資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangzhiyin/Downloads/西雙版納·普洱-7天6晚自由行攻略/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172A9F27-6122-D94E-A48A-27B2DE0DA0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05166668-989D-FC47-8264-DF4BD6500657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="每日行程明細表" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="183">
   <si>
     <t>活動名稱</t>
   </si>
@@ -599,6 +599,14 @@
   </si>
   <si>
     <t>早上 07:30</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>下午 17:40</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果景迈山不习惯，回去版纳/普洱。（最好中午12点左右能决定好）</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -744,59 +752,59 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -839,8 +847,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DailyItinerarySource" displayName="DailyItinerarySource" ref="A1:G32" totalsRowShown="0">
-  <autoFilter ref="A1:G32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DailyItinerarySource" displayName="DailyItinerarySource" ref="A1:G35" totalsRowShown="0">
+  <autoFilter ref="A1:G35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="活動名稱"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="日期"/>
@@ -1075,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27.5" style="4" customWidth="1"/>
@@ -1646,6 +1654,9 @@
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="G27" s="36" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="34" customHeight="1">
       <c r="A28" s="6" t="s">
@@ -1666,6 +1677,9 @@
       <c r="F28" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="G28" s="36" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="34" customHeight="1">
       <c r="A29" s="6" t="s">
@@ -1686,64 +1700,136 @@
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="G29" s="36" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="34" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B30" s="3">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="34" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B31" s="3">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="34" customHeight="1">
       <c r="A32" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46313</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="34" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="34" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="34" customHeight="1">
+      <c r="A35" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B35" s="3">
         <v>46314</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>77</v>
       </c>
     </row>
